--- a/BD_Bombonas.xlsx
+++ b/BD_Bombonas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupomateus-my.sharepoint.com/personal/hamilton_pires_grupomateus_com/Documents/hamilton/Consultoria/Lidiane/2026/app_bombonas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAFEE7CF-26A0-49BF-9FC1-AF19D2FCFF14}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="8_{40E215D4-4623-41EB-B246-4B63951E0A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD25099F-61A1-4F53-81B3-FDEBE2665E6C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9588DCE0-F8D9-46B8-8782-90EC7820DC70}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BASE BOMBONAS" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$808</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE BOMBONAS'!$A$1:$L$986</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="14">
   <si>
     <t>DATA</t>
   </si>
@@ -99,12 +99,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -119,9 +125,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -137,6 +145,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -459,7 +471,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:L864"/>
+  <dimension ref="A1:L986"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -30758,13 +30770,13 @@
         <v>1</v>
       </c>
       <c r="D798">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E798">
         <v>16</v>
       </c>
       <c r="F798">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="G798">
         <v>0</v>
@@ -30869,16 +30881,16 @@
         <v>2</v>
       </c>
       <c r="C801">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D801">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="E801">
         <v>7</v>
       </c>
       <c r="F801">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G801">
         <v>0</v>
@@ -30913,10 +30925,10 @@
         <v>50</v>
       </c>
       <c r="E802">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F802">
-        <v>525</v>
+        <v>500</v>
       </c>
       <c r="G802">
         <v>0</v>
@@ -33290,6 +33302,4642 @@
         <v>2</v>
       </c>
       <c r="L864">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A865" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B865" t="s">
+        <v>2</v>
+      </c>
+      <c r="C865">
+        <v>0</v>
+      </c>
+      <c r="D865">
+        <v>0</v>
+      </c>
+      <c r="E865">
+        <v>6</v>
+      </c>
+      <c r="F865">
+        <v>150</v>
+      </c>
+      <c r="G865">
+        <v>0</v>
+      </c>
+      <c r="H865">
+        <v>0</v>
+      </c>
+      <c r="I865">
+        <v>0</v>
+      </c>
+      <c r="J865">
+        <v>0</v>
+      </c>
+      <c r="K865">
+        <v>1</v>
+      </c>
+      <c r="L865">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A866" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B866" t="s">
+        <v>3</v>
+      </c>
+      <c r="C866">
+        <v>0</v>
+      </c>
+      <c r="D866">
+        <v>0</v>
+      </c>
+      <c r="E866">
+        <v>18</v>
+      </c>
+      <c r="F866">
+        <v>450</v>
+      </c>
+      <c r="G866">
+        <v>0</v>
+      </c>
+      <c r="H866">
+        <v>0</v>
+      </c>
+      <c r="I866">
+        <v>0</v>
+      </c>
+      <c r="J866">
+        <v>0</v>
+      </c>
+      <c r="K866">
+        <v>1</v>
+      </c>
+      <c r="L866">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A867" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B867" t="s">
+        <v>2</v>
+      </c>
+      <c r="C867">
+        <v>0</v>
+      </c>
+      <c r="D867">
+        <v>0</v>
+      </c>
+      <c r="E867">
+        <v>6</v>
+      </c>
+      <c r="F867">
+        <v>150</v>
+      </c>
+      <c r="G867">
+        <v>0</v>
+      </c>
+      <c r="H867">
+        <v>0</v>
+      </c>
+      <c r="I867">
+        <v>0</v>
+      </c>
+      <c r="J867">
+        <v>0</v>
+      </c>
+      <c r="K867">
+        <v>0</v>
+      </c>
+      <c r="L867">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A868" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B868" t="s">
+        <v>3</v>
+      </c>
+      <c r="C868">
+        <v>0</v>
+      </c>
+      <c r="D868">
+        <v>0</v>
+      </c>
+      <c r="E868">
+        <v>19</v>
+      </c>
+      <c r="F868">
+        <v>475</v>
+      </c>
+      <c r="G868">
+        <v>0</v>
+      </c>
+      <c r="H868">
+        <v>0</v>
+      </c>
+      <c r="I868">
+        <v>2</v>
+      </c>
+      <c r="J868">
+        <v>50</v>
+      </c>
+      <c r="K868">
+        <v>1</v>
+      </c>
+      <c r="L868">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A869" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B869" t="s">
+        <v>2</v>
+      </c>
+      <c r="C869">
+        <v>0</v>
+      </c>
+      <c r="D869">
+        <v>0</v>
+      </c>
+      <c r="E869">
+        <v>6</v>
+      </c>
+      <c r="F869">
+        <v>150</v>
+      </c>
+      <c r="G869">
+        <v>0</v>
+      </c>
+      <c r="H869">
+        <v>0</v>
+      </c>
+      <c r="I869">
+        <v>0</v>
+      </c>
+      <c r="J869">
+        <v>0</v>
+      </c>
+      <c r="K869">
+        <v>1</v>
+      </c>
+      <c r="L869">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A870" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B870" t="s">
+        <v>3</v>
+      </c>
+      <c r="C870">
+        <v>0</v>
+      </c>
+      <c r="D870">
+        <v>0</v>
+      </c>
+      <c r="E870">
+        <v>19</v>
+      </c>
+      <c r="F870">
+        <v>475</v>
+      </c>
+      <c r="G870">
+        <v>0</v>
+      </c>
+      <c r="H870">
+        <v>0</v>
+      </c>
+      <c r="I870">
+        <v>1</v>
+      </c>
+      <c r="J870">
+        <v>25</v>
+      </c>
+      <c r="K870">
+        <v>2</v>
+      </c>
+      <c r="L870">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A871" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B871" t="s">
+        <v>2</v>
+      </c>
+      <c r="C871">
+        <v>0</v>
+      </c>
+      <c r="D871">
+        <v>0</v>
+      </c>
+      <c r="E871">
+        <v>6</v>
+      </c>
+      <c r="F871">
+        <v>150</v>
+      </c>
+      <c r="G871">
+        <v>0</v>
+      </c>
+      <c r="H871">
+        <v>0</v>
+      </c>
+      <c r="I871">
+        <v>0</v>
+      </c>
+      <c r="J871">
+        <v>0</v>
+      </c>
+      <c r="K871">
+        <v>0</v>
+      </c>
+      <c r="L871">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A872" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B872" t="s">
+        <v>3</v>
+      </c>
+      <c r="C872">
+        <v>0</v>
+      </c>
+      <c r="D872">
+        <v>0</v>
+      </c>
+      <c r="E872">
+        <v>19</v>
+      </c>
+      <c r="F872">
+        <v>475</v>
+      </c>
+      <c r="G872">
+        <v>0</v>
+      </c>
+      <c r="H872">
+        <v>0</v>
+      </c>
+      <c r="I872">
+        <v>2</v>
+      </c>
+      <c r="J872">
+        <v>50</v>
+      </c>
+      <c r="K872">
+        <v>2</v>
+      </c>
+      <c r="L872">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A873" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B873" t="s">
+        <v>2</v>
+      </c>
+      <c r="C873">
+        <v>0</v>
+      </c>
+      <c r="D873">
+        <v>0</v>
+      </c>
+      <c r="E873">
+        <v>7</v>
+      </c>
+      <c r="F873">
+        <v>175</v>
+      </c>
+      <c r="G873">
+        <v>0</v>
+      </c>
+      <c r="H873">
+        <v>0</v>
+      </c>
+      <c r="I873">
+        <v>0</v>
+      </c>
+      <c r="J873">
+        <v>0</v>
+      </c>
+      <c r="K873">
+        <v>1</v>
+      </c>
+      <c r="L873">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A874" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B874" t="s">
+        <v>3</v>
+      </c>
+      <c r="C874">
+        <v>0</v>
+      </c>
+      <c r="D874">
+        <v>0</v>
+      </c>
+      <c r="E874">
+        <v>19</v>
+      </c>
+      <c r="F874">
+        <v>475</v>
+      </c>
+      <c r="G874">
+        <v>0</v>
+      </c>
+      <c r="H874">
+        <v>0</v>
+      </c>
+      <c r="I874">
+        <v>2</v>
+      </c>
+      <c r="J874">
+        <v>50</v>
+      </c>
+      <c r="K874">
+        <v>1</v>
+      </c>
+      <c r="L874">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A875" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B875" t="s">
+        <v>2</v>
+      </c>
+      <c r="C875">
+        <v>0</v>
+      </c>
+      <c r="D875">
+        <v>0</v>
+      </c>
+      <c r="E875">
+        <v>7</v>
+      </c>
+      <c r="F875">
+        <v>175</v>
+      </c>
+      <c r="G875">
+        <v>0</v>
+      </c>
+      <c r="H875">
+        <v>0</v>
+      </c>
+      <c r="I875">
+        <v>1</v>
+      </c>
+      <c r="J875">
+        <v>25</v>
+      </c>
+      <c r="K875">
+        <v>1</v>
+      </c>
+      <c r="L875">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="876" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A876" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B876" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C876" s="3">
+        <v>0</v>
+      </c>
+      <c r="D876" s="3">
+        <v>0</v>
+      </c>
+      <c r="E876" s="3">
+        <v>19</v>
+      </c>
+      <c r="F876" s="3">
+        <v>475</v>
+      </c>
+      <c r="G876" s="3">
+        <v>1</v>
+      </c>
+      <c r="H876" s="3">
+        <v>15</v>
+      </c>
+      <c r="I876" s="3">
+        <v>2</v>
+      </c>
+      <c r="J876" s="3">
+        <v>50</v>
+      </c>
+      <c r="K876" s="3">
+        <v>1</v>
+      </c>
+      <c r="L876" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A877" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B877" t="s">
+        <v>2</v>
+      </c>
+      <c r="C877">
+        <v>0</v>
+      </c>
+      <c r="D877">
+        <v>0</v>
+      </c>
+      <c r="E877">
+        <v>7</v>
+      </c>
+      <c r="F877">
+        <v>175</v>
+      </c>
+      <c r="G877">
+        <v>0</v>
+      </c>
+      <c r="H877">
+        <v>0</v>
+      </c>
+      <c r="I877">
+        <v>0</v>
+      </c>
+      <c r="J877">
+        <v>0</v>
+      </c>
+      <c r="K877">
+        <v>0</v>
+      </c>
+      <c r="L877">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A878" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B878" t="s">
+        <v>3</v>
+      </c>
+      <c r="C878">
+        <v>0</v>
+      </c>
+      <c r="D878">
+        <v>0</v>
+      </c>
+      <c r="E878">
+        <v>19</v>
+      </c>
+      <c r="F878">
+        <v>475</v>
+      </c>
+      <c r="G878">
+        <v>0</v>
+      </c>
+      <c r="H878">
+        <v>0</v>
+      </c>
+      <c r="I878">
+        <v>1</v>
+      </c>
+      <c r="J878">
+        <v>25</v>
+      </c>
+      <c r="K878">
+        <v>4</v>
+      </c>
+      <c r="L878">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A879" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B879" t="s">
+        <v>2</v>
+      </c>
+      <c r="C879">
+        <v>0</v>
+      </c>
+      <c r="D879">
+        <v>0</v>
+      </c>
+      <c r="E879">
+        <v>5</v>
+      </c>
+      <c r="F879">
+        <v>125</v>
+      </c>
+      <c r="G879">
+        <v>0</v>
+      </c>
+      <c r="H879">
+        <v>0</v>
+      </c>
+      <c r="I879">
+        <v>0</v>
+      </c>
+      <c r="J879">
+        <v>0</v>
+      </c>
+      <c r="K879">
+        <v>1</v>
+      </c>
+      <c r="L879">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A880" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B880" t="s">
+        <v>3</v>
+      </c>
+      <c r="C880">
+        <v>0</v>
+      </c>
+      <c r="D880">
+        <v>0</v>
+      </c>
+      <c r="E880">
+        <v>18</v>
+      </c>
+      <c r="F880">
+        <v>450</v>
+      </c>
+      <c r="G880">
+        <v>0</v>
+      </c>
+      <c r="H880">
+        <v>0</v>
+      </c>
+      <c r="I880">
+        <v>0</v>
+      </c>
+      <c r="J880">
+        <v>0</v>
+      </c>
+      <c r="K880">
+        <v>1</v>
+      </c>
+      <c r="L880">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A881" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B881" t="s">
+        <v>2</v>
+      </c>
+      <c r="C881">
+        <v>0</v>
+      </c>
+      <c r="D881">
+        <v>0</v>
+      </c>
+      <c r="E881">
+        <v>6</v>
+      </c>
+      <c r="F881">
+        <v>150</v>
+      </c>
+      <c r="G881">
+        <v>0</v>
+      </c>
+      <c r="H881">
+        <v>0</v>
+      </c>
+      <c r="I881">
+        <v>0</v>
+      </c>
+      <c r="J881">
+        <v>0</v>
+      </c>
+      <c r="K881">
+        <v>1</v>
+      </c>
+      <c r="L881">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A882" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B882" t="s">
+        <v>3</v>
+      </c>
+      <c r="C882">
+        <v>0</v>
+      </c>
+      <c r="D882">
+        <v>0</v>
+      </c>
+      <c r="E882">
+        <v>17</v>
+      </c>
+      <c r="F882">
+        <v>425</v>
+      </c>
+      <c r="G882">
+        <v>0</v>
+      </c>
+      <c r="H882">
+        <v>0</v>
+      </c>
+      <c r="I882">
+        <v>1</v>
+      </c>
+      <c r="J882">
+        <v>25</v>
+      </c>
+      <c r="K882">
+        <v>2</v>
+      </c>
+      <c r="L882">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A883" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B883" t="s">
+        <v>2</v>
+      </c>
+      <c r="C883">
+        <v>0</v>
+      </c>
+      <c r="D883">
+        <v>0</v>
+      </c>
+      <c r="E883">
+        <v>7</v>
+      </c>
+      <c r="F883">
+        <v>175</v>
+      </c>
+      <c r="G883">
+        <v>0</v>
+      </c>
+      <c r="H883">
+        <v>0</v>
+      </c>
+      <c r="I883">
+        <v>0</v>
+      </c>
+      <c r="J883">
+        <v>0</v>
+      </c>
+      <c r="K883">
+        <v>0</v>
+      </c>
+      <c r="L883">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A884" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B884" t="s">
+        <v>3</v>
+      </c>
+      <c r="C884">
+        <v>0</v>
+      </c>
+      <c r="D884">
+        <v>0</v>
+      </c>
+      <c r="E884">
+        <v>19</v>
+      </c>
+      <c r="F884">
+        <v>475</v>
+      </c>
+      <c r="G884">
+        <v>0</v>
+      </c>
+      <c r="H884">
+        <v>0</v>
+      </c>
+      <c r="I884">
+        <v>1</v>
+      </c>
+      <c r="J884">
+        <v>25</v>
+      </c>
+      <c r="K884">
+        <v>3</v>
+      </c>
+      <c r="L884">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A885" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B885" t="s">
+        <v>2</v>
+      </c>
+      <c r="C885">
+        <v>0</v>
+      </c>
+      <c r="D885">
+        <v>0</v>
+      </c>
+      <c r="E885">
+        <v>6</v>
+      </c>
+      <c r="F885">
+        <v>150</v>
+      </c>
+      <c r="G885">
+        <v>0</v>
+      </c>
+      <c r="H885">
+        <v>0</v>
+      </c>
+      <c r="I885">
+        <v>0</v>
+      </c>
+      <c r="J885">
+        <v>0</v>
+      </c>
+      <c r="K885">
+        <v>0</v>
+      </c>
+      <c r="L885">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A886" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B886" t="s">
+        <v>3</v>
+      </c>
+      <c r="C886">
+        <v>0</v>
+      </c>
+      <c r="D886">
+        <v>0</v>
+      </c>
+      <c r="E886">
+        <v>21</v>
+      </c>
+      <c r="F886">
+        <v>525</v>
+      </c>
+      <c r="G886">
+        <v>0</v>
+      </c>
+      <c r="H886">
+        <v>0</v>
+      </c>
+      <c r="I886">
+        <v>1</v>
+      </c>
+      <c r="J886">
+        <v>25</v>
+      </c>
+      <c r="K886">
+        <v>3</v>
+      </c>
+      <c r="L886">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A887" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B887" t="s">
+        <v>2</v>
+      </c>
+      <c r="C887">
+        <v>0</v>
+      </c>
+      <c r="D887">
+        <v>0</v>
+      </c>
+      <c r="E887">
+        <v>7</v>
+      </c>
+      <c r="F887">
+        <v>175</v>
+      </c>
+      <c r="G887">
+        <v>0</v>
+      </c>
+      <c r="H887">
+        <v>0</v>
+      </c>
+      <c r="I887">
+        <v>0</v>
+      </c>
+      <c r="J887">
+        <v>0</v>
+      </c>
+      <c r="K887">
+        <v>1</v>
+      </c>
+      <c r="L887">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A888" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B888" t="s">
+        <v>3</v>
+      </c>
+      <c r="C888">
+        <v>0</v>
+      </c>
+      <c r="D888">
+        <v>0</v>
+      </c>
+      <c r="E888">
+        <v>23</v>
+      </c>
+      <c r="F888">
+        <v>575</v>
+      </c>
+      <c r="G888">
+        <v>0</v>
+      </c>
+      <c r="H888">
+        <v>0</v>
+      </c>
+      <c r="I888">
+        <v>2</v>
+      </c>
+      <c r="J888">
+        <v>50</v>
+      </c>
+      <c r="K888">
+        <v>1</v>
+      </c>
+      <c r="L888">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A889" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B889" t="s">
+        <v>2</v>
+      </c>
+      <c r="C889">
+        <v>0</v>
+      </c>
+      <c r="D889">
+        <v>0</v>
+      </c>
+      <c r="E889">
+        <v>6</v>
+      </c>
+      <c r="F889">
+        <v>150</v>
+      </c>
+      <c r="G889">
+        <v>0</v>
+      </c>
+      <c r="H889">
+        <v>0</v>
+      </c>
+      <c r="I889">
+        <v>0</v>
+      </c>
+      <c r="J889">
+        <v>0</v>
+      </c>
+      <c r="K889">
+        <v>0</v>
+      </c>
+      <c r="L889">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A890" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B890" t="s">
+        <v>3</v>
+      </c>
+      <c r="C890">
+        <v>0</v>
+      </c>
+      <c r="D890">
+        <v>0</v>
+      </c>
+      <c r="E890">
+        <v>18</v>
+      </c>
+      <c r="F890">
+        <v>450</v>
+      </c>
+      <c r="G890">
+        <v>0</v>
+      </c>
+      <c r="H890">
+        <v>0</v>
+      </c>
+      <c r="I890">
+        <v>0</v>
+      </c>
+      <c r="J890">
+        <v>0</v>
+      </c>
+      <c r="K890">
+        <v>2</v>
+      </c>
+      <c r="L890">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A891" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B891" t="s">
+        <v>2</v>
+      </c>
+      <c r="C891">
+        <v>0</v>
+      </c>
+      <c r="D891">
+        <v>0</v>
+      </c>
+      <c r="E891">
+        <v>6</v>
+      </c>
+      <c r="F891">
+        <v>150</v>
+      </c>
+      <c r="G891">
+        <v>0</v>
+      </c>
+      <c r="H891">
+        <v>0</v>
+      </c>
+      <c r="I891">
+        <v>0</v>
+      </c>
+      <c r="J891">
+        <v>0</v>
+      </c>
+      <c r="K891">
+        <v>0</v>
+      </c>
+      <c r="L891">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A892" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B892" t="s">
+        <v>3</v>
+      </c>
+      <c r="C892">
+        <v>0</v>
+      </c>
+      <c r="D892">
+        <v>0</v>
+      </c>
+      <c r="E892">
+        <v>18</v>
+      </c>
+      <c r="F892">
+        <v>450</v>
+      </c>
+      <c r="G892">
+        <v>0</v>
+      </c>
+      <c r="H892">
+        <v>0</v>
+      </c>
+      <c r="I892">
+        <v>1</v>
+      </c>
+      <c r="J892">
+        <v>25</v>
+      </c>
+      <c r="K892">
+        <v>0</v>
+      </c>
+      <c r="L892">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A893" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B893" t="s">
+        <v>2</v>
+      </c>
+      <c r="C893">
+        <v>0</v>
+      </c>
+      <c r="D893">
+        <v>0</v>
+      </c>
+      <c r="E893">
+        <v>5</v>
+      </c>
+      <c r="F893">
+        <v>125</v>
+      </c>
+      <c r="G893">
+        <v>0</v>
+      </c>
+      <c r="H893">
+        <v>0</v>
+      </c>
+      <c r="I893">
+        <v>0</v>
+      </c>
+      <c r="J893">
+        <v>0</v>
+      </c>
+      <c r="K893">
+        <v>1</v>
+      </c>
+      <c r="L893">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A894" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B894" t="s">
+        <v>3</v>
+      </c>
+      <c r="C894">
+        <v>0</v>
+      </c>
+      <c r="D894">
+        <v>0</v>
+      </c>
+      <c r="E894">
+        <v>19</v>
+      </c>
+      <c r="F894">
+        <v>475</v>
+      </c>
+      <c r="G894">
+        <v>0</v>
+      </c>
+      <c r="H894">
+        <v>0</v>
+      </c>
+      <c r="I894">
+        <v>1</v>
+      </c>
+      <c r="J894">
+        <v>25</v>
+      </c>
+      <c r="K894">
+        <v>3</v>
+      </c>
+      <c r="L894">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A895" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B895" t="s">
+        <v>2</v>
+      </c>
+      <c r="C895">
+        <v>0</v>
+      </c>
+      <c r="D895">
+        <v>0</v>
+      </c>
+      <c r="E895">
+        <v>7</v>
+      </c>
+      <c r="F895">
+        <v>175</v>
+      </c>
+      <c r="G895">
+        <v>0</v>
+      </c>
+      <c r="H895">
+        <v>0</v>
+      </c>
+      <c r="I895">
+        <v>0</v>
+      </c>
+      <c r="J895">
+        <v>0</v>
+      </c>
+      <c r="K895">
+        <v>0</v>
+      </c>
+      <c r="L895">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A896" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B896" t="s">
+        <v>3</v>
+      </c>
+      <c r="C896">
+        <v>0</v>
+      </c>
+      <c r="D896">
+        <v>0</v>
+      </c>
+      <c r="E896">
+        <v>17</v>
+      </c>
+      <c r="F896">
+        <v>425</v>
+      </c>
+      <c r="G896">
+        <v>0</v>
+      </c>
+      <c r="H896">
+        <v>0</v>
+      </c>
+      <c r="I896">
+        <v>2</v>
+      </c>
+      <c r="J896">
+        <v>50</v>
+      </c>
+      <c r="K896">
+        <v>2</v>
+      </c>
+      <c r="L896">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A897" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B897" t="s">
+        <v>2</v>
+      </c>
+      <c r="C897">
+        <v>0</v>
+      </c>
+      <c r="D897">
+        <v>0</v>
+      </c>
+      <c r="E897">
+        <v>6</v>
+      </c>
+      <c r="F897">
+        <v>150</v>
+      </c>
+      <c r="G897">
+        <v>0</v>
+      </c>
+      <c r="H897">
+        <v>0</v>
+      </c>
+      <c r="I897">
+        <v>0</v>
+      </c>
+      <c r="J897">
+        <v>0</v>
+      </c>
+      <c r="K897">
+        <v>0</v>
+      </c>
+      <c r="L897">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A898" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B898" t="s">
+        <v>3</v>
+      </c>
+      <c r="C898">
+        <v>0</v>
+      </c>
+      <c r="D898">
+        <v>0</v>
+      </c>
+      <c r="E898">
+        <v>20</v>
+      </c>
+      <c r="F898">
+        <v>500</v>
+      </c>
+      <c r="G898">
+        <v>0</v>
+      </c>
+      <c r="H898">
+        <v>0</v>
+      </c>
+      <c r="I898">
+        <v>1</v>
+      </c>
+      <c r="J898">
+        <v>25</v>
+      </c>
+      <c r="K898">
+        <v>1</v>
+      </c>
+      <c r="L898">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A899" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B899" t="s">
+        <v>2</v>
+      </c>
+      <c r="C899">
+        <v>0</v>
+      </c>
+      <c r="D899">
+        <v>0</v>
+      </c>
+      <c r="E899">
+        <v>5</v>
+      </c>
+      <c r="F899">
+        <v>125</v>
+      </c>
+      <c r="G899">
+        <v>0</v>
+      </c>
+      <c r="H899">
+        <v>0</v>
+      </c>
+      <c r="I899">
+        <v>0</v>
+      </c>
+      <c r="J899">
+        <v>0</v>
+      </c>
+      <c r="K899">
+        <v>1</v>
+      </c>
+      <c r="L899">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A900" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B900" t="s">
+        <v>3</v>
+      </c>
+      <c r="C900">
+        <v>0</v>
+      </c>
+      <c r="D900">
+        <v>0</v>
+      </c>
+      <c r="E900">
+        <v>18</v>
+      </c>
+      <c r="F900">
+        <v>450</v>
+      </c>
+      <c r="G900">
+        <v>0</v>
+      </c>
+      <c r="H900">
+        <v>0</v>
+      </c>
+      <c r="I900">
+        <v>1</v>
+      </c>
+      <c r="J900">
+        <v>25</v>
+      </c>
+      <c r="K900">
+        <v>3</v>
+      </c>
+      <c r="L900">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A901" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B901" t="s">
+        <v>2</v>
+      </c>
+      <c r="C901">
+        <v>0</v>
+      </c>
+      <c r="D901">
+        <v>0</v>
+      </c>
+      <c r="E901">
+        <v>6</v>
+      </c>
+      <c r="F901">
+        <v>150</v>
+      </c>
+      <c r="G901">
+        <v>0</v>
+      </c>
+      <c r="H901">
+        <v>0</v>
+      </c>
+      <c r="I901">
+        <v>0</v>
+      </c>
+      <c r="J901">
+        <v>0</v>
+      </c>
+      <c r="K901">
+        <v>0</v>
+      </c>
+      <c r="L901">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A902" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B902" t="s">
+        <v>3</v>
+      </c>
+      <c r="C902">
+        <v>0</v>
+      </c>
+      <c r="D902">
+        <v>0</v>
+      </c>
+      <c r="E902">
+        <v>19</v>
+      </c>
+      <c r="F902">
+        <v>475</v>
+      </c>
+      <c r="G902">
+        <v>0</v>
+      </c>
+      <c r="H902">
+        <v>0</v>
+      </c>
+      <c r="I902">
+        <v>2</v>
+      </c>
+      <c r="J902">
+        <v>50</v>
+      </c>
+      <c r="K902">
+        <v>1</v>
+      </c>
+      <c r="L902">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A903" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B903" t="s">
+        <v>2</v>
+      </c>
+      <c r="C903">
+        <v>0</v>
+      </c>
+      <c r="D903">
+        <v>0</v>
+      </c>
+      <c r="E903">
+        <v>8</v>
+      </c>
+      <c r="F903">
+        <v>200</v>
+      </c>
+      <c r="G903">
+        <v>0</v>
+      </c>
+      <c r="H903">
+        <v>0</v>
+      </c>
+      <c r="I903">
+        <v>0</v>
+      </c>
+      <c r="J903">
+        <v>0</v>
+      </c>
+      <c r="K903">
+        <v>1</v>
+      </c>
+      <c r="L903">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A904" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B904" t="s">
+        <v>3</v>
+      </c>
+      <c r="C904">
+        <v>0</v>
+      </c>
+      <c r="D904">
+        <v>0</v>
+      </c>
+      <c r="E904">
+        <v>17</v>
+      </c>
+      <c r="F904">
+        <v>425</v>
+      </c>
+      <c r="G904">
+        <v>1</v>
+      </c>
+      <c r="H904">
+        <v>15</v>
+      </c>
+      <c r="I904">
+        <v>1</v>
+      </c>
+      <c r="J904">
+        <v>25</v>
+      </c>
+      <c r="K904">
+        <v>2</v>
+      </c>
+      <c r="L904">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A905" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B905" t="s">
+        <v>2</v>
+      </c>
+      <c r="C905">
+        <v>0</v>
+      </c>
+      <c r="D905">
+        <v>0</v>
+      </c>
+      <c r="E905">
+        <v>6</v>
+      </c>
+      <c r="F905">
+        <v>150</v>
+      </c>
+      <c r="G905">
+        <v>0</v>
+      </c>
+      <c r="H905">
+        <v>0</v>
+      </c>
+      <c r="I905">
+        <v>0</v>
+      </c>
+      <c r="J905">
+        <v>0</v>
+      </c>
+      <c r="K905">
+        <v>1</v>
+      </c>
+      <c r="L905">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A906" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B906" t="s">
+        <v>3</v>
+      </c>
+      <c r="C906">
+        <v>0</v>
+      </c>
+      <c r="D906">
+        <v>0</v>
+      </c>
+      <c r="E906">
+        <v>17</v>
+      </c>
+      <c r="F906">
+        <v>425</v>
+      </c>
+      <c r="G906">
+        <v>0</v>
+      </c>
+      <c r="H906">
+        <v>0</v>
+      </c>
+      <c r="I906">
+        <v>1</v>
+      </c>
+      <c r="J906">
+        <v>25</v>
+      </c>
+      <c r="K906">
+        <v>1</v>
+      </c>
+      <c r="L906">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A907" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B907" t="s">
+        <v>2</v>
+      </c>
+      <c r="C907">
+        <v>0</v>
+      </c>
+      <c r="D907">
+        <v>0</v>
+      </c>
+      <c r="E907">
+        <v>6</v>
+      </c>
+      <c r="F907">
+        <v>150</v>
+      </c>
+      <c r="G907">
+        <v>0</v>
+      </c>
+      <c r="H907">
+        <v>0</v>
+      </c>
+      <c r="I907">
+        <v>0</v>
+      </c>
+      <c r="J907">
+        <v>0</v>
+      </c>
+      <c r="K907">
+        <v>0</v>
+      </c>
+      <c r="L907">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A908" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B908" t="s">
+        <v>3</v>
+      </c>
+      <c r="C908">
+        <v>0</v>
+      </c>
+      <c r="D908">
+        <v>0</v>
+      </c>
+      <c r="E908">
+        <v>20</v>
+      </c>
+      <c r="F908">
+        <v>500</v>
+      </c>
+      <c r="G908">
+        <v>0</v>
+      </c>
+      <c r="H908">
+        <v>0</v>
+      </c>
+      <c r="I908">
+        <v>1</v>
+      </c>
+      <c r="J908">
+        <v>25</v>
+      </c>
+      <c r="K908">
+        <v>2</v>
+      </c>
+      <c r="L908">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A909" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B909" t="s">
+        <v>2</v>
+      </c>
+      <c r="C909">
+        <v>0</v>
+      </c>
+      <c r="D909">
+        <v>0</v>
+      </c>
+      <c r="E909">
+        <v>6</v>
+      </c>
+      <c r="F909">
+        <v>150</v>
+      </c>
+      <c r="G909">
+        <v>0</v>
+      </c>
+      <c r="H909">
+        <v>0</v>
+      </c>
+      <c r="I909">
+        <v>0</v>
+      </c>
+      <c r="J909">
+        <v>0</v>
+      </c>
+      <c r="K909">
+        <v>1</v>
+      </c>
+      <c r="L909">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A910" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B910" t="s">
+        <v>3</v>
+      </c>
+      <c r="C910">
+        <v>0</v>
+      </c>
+      <c r="D910">
+        <v>0</v>
+      </c>
+      <c r="E910">
+        <v>16</v>
+      </c>
+      <c r="F910">
+        <v>400</v>
+      </c>
+      <c r="G910">
+        <v>0</v>
+      </c>
+      <c r="H910">
+        <v>0</v>
+      </c>
+      <c r="I910">
+        <v>2</v>
+      </c>
+      <c r="J910">
+        <v>50</v>
+      </c>
+      <c r="K910">
+        <v>3</v>
+      </c>
+      <c r="L910">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A911" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B911" t="s">
+        <v>2</v>
+      </c>
+      <c r="C911">
+        <v>0</v>
+      </c>
+      <c r="D911">
+        <v>0</v>
+      </c>
+      <c r="E911">
+        <v>8</v>
+      </c>
+      <c r="F911">
+        <v>200</v>
+      </c>
+      <c r="G911">
+        <v>0</v>
+      </c>
+      <c r="H911">
+        <v>0</v>
+      </c>
+      <c r="I911">
+        <v>0</v>
+      </c>
+      <c r="J911">
+        <v>0</v>
+      </c>
+      <c r="K911">
+        <v>1</v>
+      </c>
+      <c r="L911">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A912" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B912" t="s">
+        <v>3</v>
+      </c>
+      <c r="C912">
+        <v>0</v>
+      </c>
+      <c r="D912">
+        <v>0</v>
+      </c>
+      <c r="E912">
+        <v>17</v>
+      </c>
+      <c r="F912">
+        <v>425</v>
+      </c>
+      <c r="G912">
+        <v>0</v>
+      </c>
+      <c r="H912">
+        <v>0</v>
+      </c>
+      <c r="I912">
+        <v>2</v>
+      </c>
+      <c r="J912">
+        <v>50</v>
+      </c>
+      <c r="K912">
+        <v>2</v>
+      </c>
+      <c r="L912">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A913" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B913" t="s">
+        <v>2</v>
+      </c>
+      <c r="C913">
+        <v>0</v>
+      </c>
+      <c r="D913">
+        <v>0</v>
+      </c>
+      <c r="E913">
+        <v>6</v>
+      </c>
+      <c r="F913">
+        <v>150</v>
+      </c>
+      <c r="G913">
+        <v>0</v>
+      </c>
+      <c r="H913">
+        <v>0</v>
+      </c>
+      <c r="I913">
+        <v>0</v>
+      </c>
+      <c r="J913">
+        <v>0</v>
+      </c>
+      <c r="K913">
+        <v>0</v>
+      </c>
+      <c r="L913">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A914" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B914" t="s">
+        <v>3</v>
+      </c>
+      <c r="C914">
+        <v>0</v>
+      </c>
+      <c r="D914">
+        <v>0</v>
+      </c>
+      <c r="E914">
+        <v>17</v>
+      </c>
+      <c r="F914">
+        <v>425</v>
+      </c>
+      <c r="G914">
+        <v>0</v>
+      </c>
+      <c r="H914">
+        <v>0</v>
+      </c>
+      <c r="I914">
+        <v>3</v>
+      </c>
+      <c r="J914">
+        <v>75</v>
+      </c>
+      <c r="K914">
+        <v>2</v>
+      </c>
+      <c r="L914">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A915" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B915" t="s">
+        <v>2</v>
+      </c>
+      <c r="C915">
+        <v>0</v>
+      </c>
+      <c r="D915">
+        <v>0</v>
+      </c>
+      <c r="E915">
+        <v>7</v>
+      </c>
+      <c r="F915">
+        <v>175</v>
+      </c>
+      <c r="G915">
+        <v>0</v>
+      </c>
+      <c r="H915">
+        <v>0</v>
+      </c>
+      <c r="I915">
+        <v>0</v>
+      </c>
+      <c r="J915">
+        <v>0</v>
+      </c>
+      <c r="K915">
+        <v>0</v>
+      </c>
+      <c r="L915">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A916" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B916" t="s">
+        <v>3</v>
+      </c>
+      <c r="C916">
+        <v>0</v>
+      </c>
+      <c r="D916">
+        <v>0</v>
+      </c>
+      <c r="E916">
+        <v>19</v>
+      </c>
+      <c r="F916">
+        <v>475</v>
+      </c>
+      <c r="G916">
+        <v>0</v>
+      </c>
+      <c r="H916">
+        <v>0</v>
+      </c>
+      <c r="I916">
+        <v>0</v>
+      </c>
+      <c r="J916">
+        <v>0</v>
+      </c>
+      <c r="K916">
+        <v>2</v>
+      </c>
+      <c r="L916">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A917" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B917" t="s">
+        <v>2</v>
+      </c>
+      <c r="C917">
+        <v>0</v>
+      </c>
+      <c r="D917">
+        <v>0</v>
+      </c>
+      <c r="E917">
+        <v>7</v>
+      </c>
+      <c r="F917">
+        <v>175</v>
+      </c>
+      <c r="G917">
+        <v>0</v>
+      </c>
+      <c r="H917">
+        <v>0</v>
+      </c>
+      <c r="I917">
+        <v>0</v>
+      </c>
+      <c r="J917">
+        <v>0</v>
+      </c>
+      <c r="K917">
+        <v>1</v>
+      </c>
+      <c r="L917">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A918" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B918" t="s">
+        <v>3</v>
+      </c>
+      <c r="C918">
+        <v>0</v>
+      </c>
+      <c r="D918">
+        <v>0</v>
+      </c>
+      <c r="E918">
+        <v>19</v>
+      </c>
+      <c r="F918">
+        <v>475</v>
+      </c>
+      <c r="G918">
+        <v>0</v>
+      </c>
+      <c r="H918">
+        <v>0</v>
+      </c>
+      <c r="I918">
+        <v>2</v>
+      </c>
+      <c r="J918">
+        <v>50</v>
+      </c>
+      <c r="K918">
+        <v>3</v>
+      </c>
+      <c r="L918">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A919" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B919" t="s">
+        <v>2</v>
+      </c>
+      <c r="C919">
+        <v>0</v>
+      </c>
+      <c r="D919">
+        <v>0</v>
+      </c>
+      <c r="E919">
+        <v>6</v>
+      </c>
+      <c r="F919">
+        <v>150</v>
+      </c>
+      <c r="G919">
+        <v>0</v>
+      </c>
+      <c r="H919">
+        <v>0</v>
+      </c>
+      <c r="I919">
+        <v>0</v>
+      </c>
+      <c r="J919">
+        <v>0</v>
+      </c>
+      <c r="K919">
+        <v>1</v>
+      </c>
+      <c r="L919">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A920" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B920" t="s">
+        <v>3</v>
+      </c>
+      <c r="C920">
+        <v>0</v>
+      </c>
+      <c r="D920">
+        <v>0</v>
+      </c>
+      <c r="E920">
+        <v>14</v>
+      </c>
+      <c r="F920">
+        <v>350</v>
+      </c>
+      <c r="G920">
+        <v>0</v>
+      </c>
+      <c r="H920">
+        <v>0</v>
+      </c>
+      <c r="I920">
+        <v>1</v>
+      </c>
+      <c r="J920">
+        <v>25</v>
+      </c>
+      <c r="K920">
+        <v>1</v>
+      </c>
+      <c r="L920">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A921" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B921" t="s">
+        <v>2</v>
+      </c>
+      <c r="C921">
+        <v>0</v>
+      </c>
+      <c r="D921">
+        <v>0</v>
+      </c>
+      <c r="E921">
+        <v>5</v>
+      </c>
+      <c r="F921">
+        <v>125</v>
+      </c>
+      <c r="G921">
+        <v>0</v>
+      </c>
+      <c r="H921">
+        <v>0</v>
+      </c>
+      <c r="I921">
+        <v>0</v>
+      </c>
+      <c r="J921">
+        <v>0</v>
+      </c>
+      <c r="K921">
+        <v>0</v>
+      </c>
+      <c r="L921">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A922" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B922" t="s">
+        <v>3</v>
+      </c>
+      <c r="C922">
+        <v>0</v>
+      </c>
+      <c r="D922">
+        <v>0</v>
+      </c>
+      <c r="E922">
+        <v>16</v>
+      </c>
+      <c r="F922">
+        <v>400</v>
+      </c>
+      <c r="G922">
+        <v>0</v>
+      </c>
+      <c r="H922">
+        <v>0</v>
+      </c>
+      <c r="I922">
+        <v>1</v>
+      </c>
+      <c r="J922">
+        <v>25</v>
+      </c>
+      <c r="K922">
+        <v>3</v>
+      </c>
+      <c r="L922">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A923" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B923" t="s">
+        <v>2</v>
+      </c>
+      <c r="C923">
+        <v>0</v>
+      </c>
+      <c r="D923">
+        <v>0</v>
+      </c>
+      <c r="E923">
+        <v>8</v>
+      </c>
+      <c r="F923">
+        <v>200</v>
+      </c>
+      <c r="G923">
+        <v>0</v>
+      </c>
+      <c r="H923">
+        <v>0</v>
+      </c>
+      <c r="I923">
+        <v>0</v>
+      </c>
+      <c r="J923">
+        <v>0</v>
+      </c>
+      <c r="K923">
+        <v>1</v>
+      </c>
+      <c r="L923">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A924" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B924" t="s">
+        <v>3</v>
+      </c>
+      <c r="C924">
+        <v>0</v>
+      </c>
+      <c r="D924">
+        <v>0</v>
+      </c>
+      <c r="E924">
+        <v>18</v>
+      </c>
+      <c r="F924">
+        <v>450</v>
+      </c>
+      <c r="G924">
+        <v>0</v>
+      </c>
+      <c r="H924">
+        <v>0</v>
+      </c>
+      <c r="I924">
+        <v>2</v>
+      </c>
+      <c r="J924">
+        <v>50</v>
+      </c>
+      <c r="K924">
+        <v>2</v>
+      </c>
+      <c r="L924">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A925" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B925" t="s">
+        <v>2</v>
+      </c>
+      <c r="C925">
+        <v>0</v>
+      </c>
+      <c r="D925">
+        <v>0</v>
+      </c>
+      <c r="E925">
+        <v>6</v>
+      </c>
+      <c r="F925">
+        <v>150</v>
+      </c>
+      <c r="G925">
+        <v>0</v>
+      </c>
+      <c r="H925">
+        <v>0</v>
+      </c>
+      <c r="I925">
+        <v>0</v>
+      </c>
+      <c r="J925">
+        <v>0</v>
+      </c>
+      <c r="K925">
+        <v>0</v>
+      </c>
+      <c r="L925">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A926" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B926" t="s">
+        <v>3</v>
+      </c>
+      <c r="C926">
+        <v>0</v>
+      </c>
+      <c r="D926">
+        <v>0</v>
+      </c>
+      <c r="E926">
+        <v>20</v>
+      </c>
+      <c r="F926">
+        <v>500</v>
+      </c>
+      <c r="G926">
+        <v>0</v>
+      </c>
+      <c r="H926">
+        <v>0</v>
+      </c>
+      <c r="I926">
+        <v>1</v>
+      </c>
+      <c r="J926">
+        <v>25</v>
+      </c>
+      <c r="K926">
+        <v>1</v>
+      </c>
+      <c r="L926">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A927" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B927" t="s">
+        <v>2</v>
+      </c>
+      <c r="C927">
+        <v>0</v>
+      </c>
+      <c r="D927">
+        <v>0</v>
+      </c>
+      <c r="E927">
+        <v>7</v>
+      </c>
+      <c r="F927">
+        <v>175</v>
+      </c>
+      <c r="G927">
+        <v>0</v>
+      </c>
+      <c r="H927">
+        <v>0</v>
+      </c>
+      <c r="I927">
+        <v>0</v>
+      </c>
+      <c r="J927">
+        <v>0</v>
+      </c>
+      <c r="K927">
+        <v>0</v>
+      </c>
+      <c r="L927">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A928" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B928" t="s">
+        <v>3</v>
+      </c>
+      <c r="C928">
+        <v>0</v>
+      </c>
+      <c r="D928">
+        <v>0</v>
+      </c>
+      <c r="E928">
+        <v>23</v>
+      </c>
+      <c r="F928">
+        <v>575</v>
+      </c>
+      <c r="G928">
+        <v>0</v>
+      </c>
+      <c r="H928">
+        <v>0</v>
+      </c>
+      <c r="I928">
+        <v>2</v>
+      </c>
+      <c r="J928">
+        <v>50</v>
+      </c>
+      <c r="K928">
+        <v>3</v>
+      </c>
+      <c r="L928">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A929" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B929" t="s">
+        <v>2</v>
+      </c>
+      <c r="C929">
+        <v>0</v>
+      </c>
+      <c r="D929">
+        <v>0</v>
+      </c>
+      <c r="E929">
+        <v>6</v>
+      </c>
+      <c r="F929">
+        <v>150</v>
+      </c>
+      <c r="G929">
+        <v>0</v>
+      </c>
+      <c r="H929">
+        <v>0</v>
+      </c>
+      <c r="I929">
+        <v>0</v>
+      </c>
+      <c r="J929">
+        <v>0</v>
+      </c>
+      <c r="K929">
+        <v>1</v>
+      </c>
+      <c r="L929">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A930" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B930" t="s">
+        <v>3</v>
+      </c>
+      <c r="C930">
+        <v>0</v>
+      </c>
+      <c r="D930">
+        <v>0</v>
+      </c>
+      <c r="E930">
+        <v>18</v>
+      </c>
+      <c r="F930">
+        <v>450</v>
+      </c>
+      <c r="G930">
+        <v>0</v>
+      </c>
+      <c r="H930">
+        <v>0</v>
+      </c>
+      <c r="I930">
+        <v>2</v>
+      </c>
+      <c r="J930">
+        <v>50</v>
+      </c>
+      <c r="K930">
+        <v>2</v>
+      </c>
+      <c r="L930">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A931" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B931" t="s">
+        <v>2</v>
+      </c>
+      <c r="C931">
+        <v>0</v>
+      </c>
+      <c r="D931">
+        <v>0</v>
+      </c>
+      <c r="E931">
+        <v>6</v>
+      </c>
+      <c r="F931">
+        <v>150</v>
+      </c>
+      <c r="G931">
+        <v>0</v>
+      </c>
+      <c r="H931">
+        <v>0</v>
+      </c>
+      <c r="I931">
+        <v>0</v>
+      </c>
+      <c r="J931">
+        <v>0</v>
+      </c>
+      <c r="K931">
+        <v>0</v>
+      </c>
+      <c r="L931">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A932" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B932" t="s">
+        <v>3</v>
+      </c>
+      <c r="C932">
+        <v>0</v>
+      </c>
+      <c r="D932">
+        <v>0</v>
+      </c>
+      <c r="E932">
+        <v>18</v>
+      </c>
+      <c r="F932">
+        <v>450</v>
+      </c>
+      <c r="G932">
+        <v>1</v>
+      </c>
+      <c r="H932">
+        <v>15</v>
+      </c>
+      <c r="I932">
+        <v>1</v>
+      </c>
+      <c r="J932">
+        <v>25</v>
+      </c>
+      <c r="K932">
+        <v>3</v>
+      </c>
+      <c r="L932">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A933" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B933" t="s">
+        <v>2</v>
+      </c>
+      <c r="C933">
+        <v>0</v>
+      </c>
+      <c r="D933">
+        <v>0</v>
+      </c>
+      <c r="E933">
+        <v>6</v>
+      </c>
+      <c r="F933">
+        <v>150</v>
+      </c>
+      <c r="G933">
+        <v>0</v>
+      </c>
+      <c r="H933">
+        <v>0</v>
+      </c>
+      <c r="I933">
+        <v>0</v>
+      </c>
+      <c r="J933">
+        <v>0</v>
+      </c>
+      <c r="K933">
+        <v>1</v>
+      </c>
+      <c r="L933">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A934" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B934" t="s">
+        <v>3</v>
+      </c>
+      <c r="C934">
+        <v>0</v>
+      </c>
+      <c r="D934">
+        <v>0</v>
+      </c>
+      <c r="E934">
+        <v>16</v>
+      </c>
+      <c r="F934">
+        <v>400</v>
+      </c>
+      <c r="G934">
+        <v>0</v>
+      </c>
+      <c r="H934">
+        <v>0</v>
+      </c>
+      <c r="I934">
+        <v>2</v>
+      </c>
+      <c r="J934">
+        <v>50</v>
+      </c>
+      <c r="K934">
+        <v>2</v>
+      </c>
+      <c r="L934">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A935" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B935" t="s">
+        <v>2</v>
+      </c>
+      <c r="C935">
+        <v>0</v>
+      </c>
+      <c r="D935">
+        <v>0</v>
+      </c>
+      <c r="E935">
+        <v>6</v>
+      </c>
+      <c r="F935">
+        <v>150</v>
+      </c>
+      <c r="G935">
+        <v>0</v>
+      </c>
+      <c r="H935">
+        <v>0</v>
+      </c>
+      <c r="I935">
+        <v>0</v>
+      </c>
+      <c r="J935">
+        <v>0</v>
+      </c>
+      <c r="K935">
+        <v>0</v>
+      </c>
+      <c r="L935">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A936" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B936" t="s">
+        <v>3</v>
+      </c>
+      <c r="C936">
+        <v>0</v>
+      </c>
+      <c r="D936">
+        <v>0</v>
+      </c>
+      <c r="E936">
+        <v>19</v>
+      </c>
+      <c r="F936">
+        <v>475</v>
+      </c>
+      <c r="G936">
+        <v>0</v>
+      </c>
+      <c r="H936">
+        <v>0</v>
+      </c>
+      <c r="I936">
+        <v>0</v>
+      </c>
+      <c r="J936">
+        <v>0</v>
+      </c>
+      <c r="K936">
+        <v>2</v>
+      </c>
+      <c r="L936">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A937" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B937" t="s">
+        <v>2</v>
+      </c>
+      <c r="C937">
+        <v>0</v>
+      </c>
+      <c r="D937">
+        <v>0</v>
+      </c>
+      <c r="E937">
+        <v>6</v>
+      </c>
+      <c r="F937">
+        <v>150</v>
+      </c>
+      <c r="G937">
+        <v>0</v>
+      </c>
+      <c r="H937">
+        <v>0</v>
+      </c>
+      <c r="I937">
+        <v>0</v>
+      </c>
+      <c r="J937">
+        <v>0</v>
+      </c>
+      <c r="K937">
+        <v>0</v>
+      </c>
+      <c r="L937">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A938" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B938" t="s">
+        <v>3</v>
+      </c>
+      <c r="C938">
+        <v>0</v>
+      </c>
+      <c r="D938">
+        <v>0</v>
+      </c>
+      <c r="E938">
+        <v>17</v>
+      </c>
+      <c r="F938">
+        <v>425</v>
+      </c>
+      <c r="G938">
+        <v>1</v>
+      </c>
+      <c r="H938">
+        <v>15</v>
+      </c>
+      <c r="I938">
+        <v>1</v>
+      </c>
+      <c r="J938">
+        <v>25</v>
+      </c>
+      <c r="K938">
+        <v>1</v>
+      </c>
+      <c r="L938">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A939" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B939" t="s">
+        <v>2</v>
+      </c>
+      <c r="C939">
+        <v>0</v>
+      </c>
+      <c r="D939">
+        <v>0</v>
+      </c>
+      <c r="E939">
+        <v>5</v>
+      </c>
+      <c r="F939">
+        <v>125</v>
+      </c>
+      <c r="G939">
+        <v>0</v>
+      </c>
+      <c r="H939">
+        <v>0</v>
+      </c>
+      <c r="I939">
+        <v>0</v>
+      </c>
+      <c r="J939">
+        <v>0</v>
+      </c>
+      <c r="K939">
+        <v>1</v>
+      </c>
+      <c r="L939">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A940" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B940" t="s">
+        <v>3</v>
+      </c>
+      <c r="C940">
+        <v>0</v>
+      </c>
+      <c r="D940">
+        <v>0</v>
+      </c>
+      <c r="E940">
+        <v>19</v>
+      </c>
+      <c r="F940">
+        <v>475</v>
+      </c>
+      <c r="G940">
+        <v>0</v>
+      </c>
+      <c r="H940">
+        <v>0</v>
+      </c>
+      <c r="I940">
+        <v>2</v>
+      </c>
+      <c r="J940">
+        <v>50</v>
+      </c>
+      <c r="K940">
+        <v>3</v>
+      </c>
+      <c r="L940">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A941" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B941" t="s">
+        <v>2</v>
+      </c>
+      <c r="C941">
+        <v>0</v>
+      </c>
+      <c r="D941">
+        <v>0</v>
+      </c>
+      <c r="E941">
+        <v>7</v>
+      </c>
+      <c r="F941">
+        <v>175</v>
+      </c>
+      <c r="G941">
+        <v>0</v>
+      </c>
+      <c r="H941">
+        <v>0</v>
+      </c>
+      <c r="I941">
+        <v>0</v>
+      </c>
+      <c r="J941">
+        <v>0</v>
+      </c>
+      <c r="K941">
+        <v>0</v>
+      </c>
+      <c r="L941">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A942" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B942" t="s">
+        <v>3</v>
+      </c>
+      <c r="C942">
+        <v>0</v>
+      </c>
+      <c r="D942">
+        <v>0</v>
+      </c>
+      <c r="E942">
+        <v>18</v>
+      </c>
+      <c r="F942">
+        <v>450</v>
+      </c>
+      <c r="G942">
+        <v>0</v>
+      </c>
+      <c r="H942">
+        <v>0</v>
+      </c>
+      <c r="I942">
+        <v>1</v>
+      </c>
+      <c r="J942">
+        <v>25</v>
+      </c>
+      <c r="K942">
+        <v>2</v>
+      </c>
+      <c r="L942">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A943" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B943" t="s">
+        <v>2</v>
+      </c>
+      <c r="C943">
+        <v>0</v>
+      </c>
+      <c r="D943">
+        <v>0</v>
+      </c>
+      <c r="E943">
+        <v>6</v>
+      </c>
+      <c r="F943">
+        <v>150</v>
+      </c>
+      <c r="G943">
+        <v>0</v>
+      </c>
+      <c r="H943">
+        <v>0</v>
+      </c>
+      <c r="I943">
+        <v>0</v>
+      </c>
+      <c r="J943">
+        <v>0</v>
+      </c>
+      <c r="K943">
+        <v>0</v>
+      </c>
+      <c r="L943">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A944" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B944" t="s">
+        <v>3</v>
+      </c>
+      <c r="C944">
+        <v>0</v>
+      </c>
+      <c r="D944">
+        <v>0</v>
+      </c>
+      <c r="E944">
+        <v>19</v>
+      </c>
+      <c r="F944">
+        <v>475</v>
+      </c>
+      <c r="G944">
+        <v>0</v>
+      </c>
+      <c r="H944">
+        <v>0</v>
+      </c>
+      <c r="I944">
+        <v>2</v>
+      </c>
+      <c r="J944">
+        <v>50</v>
+      </c>
+      <c r="K944">
+        <v>2</v>
+      </c>
+      <c r="L944">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A945" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B945" t="s">
+        <v>2</v>
+      </c>
+      <c r="C945">
+        <v>0</v>
+      </c>
+      <c r="D945">
+        <v>0</v>
+      </c>
+      <c r="E945">
+        <v>5</v>
+      </c>
+      <c r="F945">
+        <v>125</v>
+      </c>
+      <c r="G945">
+        <v>0</v>
+      </c>
+      <c r="H945">
+        <v>0</v>
+      </c>
+      <c r="I945">
+        <v>0</v>
+      </c>
+      <c r="J945">
+        <v>0</v>
+      </c>
+      <c r="K945">
+        <v>0</v>
+      </c>
+      <c r="L945">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A946" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B946" t="s">
+        <v>3</v>
+      </c>
+      <c r="C946">
+        <v>0</v>
+      </c>
+      <c r="D946">
+        <v>0</v>
+      </c>
+      <c r="E946">
+        <v>13</v>
+      </c>
+      <c r="F946">
+        <v>325</v>
+      </c>
+      <c r="G946">
+        <v>0</v>
+      </c>
+      <c r="H946">
+        <v>0</v>
+      </c>
+      <c r="I946">
+        <v>1</v>
+      </c>
+      <c r="J946">
+        <v>25</v>
+      </c>
+      <c r="K946">
+        <v>2</v>
+      </c>
+      <c r="L946">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A947" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B947" t="s">
+        <v>2</v>
+      </c>
+      <c r="C947">
+        <v>0</v>
+      </c>
+      <c r="D947">
+        <v>0</v>
+      </c>
+      <c r="E947">
+        <v>8</v>
+      </c>
+      <c r="F947">
+        <v>200</v>
+      </c>
+      <c r="G947">
+        <v>0</v>
+      </c>
+      <c r="H947">
+        <v>0</v>
+      </c>
+      <c r="I947">
+        <v>0</v>
+      </c>
+      <c r="J947">
+        <v>0</v>
+      </c>
+      <c r="K947">
+        <v>1</v>
+      </c>
+      <c r="L947">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A948" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B948" t="s">
+        <v>3</v>
+      </c>
+      <c r="C948">
+        <v>0</v>
+      </c>
+      <c r="D948">
+        <v>0</v>
+      </c>
+      <c r="E948">
+        <v>22</v>
+      </c>
+      <c r="F948">
+        <v>550</v>
+      </c>
+      <c r="G948">
+        <v>0</v>
+      </c>
+      <c r="H948">
+        <v>0</v>
+      </c>
+      <c r="I948">
+        <v>0</v>
+      </c>
+      <c r="J948">
+        <v>0</v>
+      </c>
+      <c r="K948">
+        <v>3</v>
+      </c>
+      <c r="L948">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A949" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B949" t="s">
+        <v>2</v>
+      </c>
+      <c r="C949">
+        <v>0</v>
+      </c>
+      <c r="D949">
+        <v>0</v>
+      </c>
+      <c r="E949">
+        <v>6</v>
+      </c>
+      <c r="F949">
+        <v>150</v>
+      </c>
+      <c r="G949">
+        <v>0</v>
+      </c>
+      <c r="H949">
+        <v>0</v>
+      </c>
+      <c r="I949">
+        <v>0</v>
+      </c>
+      <c r="J949">
+        <v>0</v>
+      </c>
+      <c r="K949">
+        <v>0</v>
+      </c>
+      <c r="L949">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A950" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B950" t="s">
+        <v>3</v>
+      </c>
+      <c r="C950">
+        <v>0</v>
+      </c>
+      <c r="D950">
+        <v>0</v>
+      </c>
+      <c r="E950">
+        <v>27</v>
+      </c>
+      <c r="F950">
+        <v>675</v>
+      </c>
+      <c r="G950">
+        <v>0</v>
+      </c>
+      <c r="H950">
+        <v>0</v>
+      </c>
+      <c r="I950">
+        <v>1</v>
+      </c>
+      <c r="J950">
+        <v>25</v>
+      </c>
+      <c r="K950">
+        <v>3</v>
+      </c>
+      <c r="L950">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A951" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B951" t="s">
+        <v>2</v>
+      </c>
+      <c r="C951">
+        <v>0</v>
+      </c>
+      <c r="D951">
+        <v>0</v>
+      </c>
+      <c r="E951">
+        <v>6</v>
+      </c>
+      <c r="F951">
+        <v>150</v>
+      </c>
+      <c r="G951">
+        <v>0</v>
+      </c>
+      <c r="H951">
+        <v>0</v>
+      </c>
+      <c r="I951">
+        <v>0</v>
+      </c>
+      <c r="J951">
+        <v>0</v>
+      </c>
+      <c r="K951">
+        <v>0</v>
+      </c>
+      <c r="L951">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A952" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B952" t="s">
+        <v>3</v>
+      </c>
+      <c r="C952">
+        <v>0</v>
+      </c>
+      <c r="D952">
+        <v>0</v>
+      </c>
+      <c r="E952">
+        <v>21</v>
+      </c>
+      <c r="F952">
+        <v>525</v>
+      </c>
+      <c r="G952">
+        <v>0</v>
+      </c>
+      <c r="H952">
+        <v>0</v>
+      </c>
+      <c r="I952">
+        <v>2</v>
+      </c>
+      <c r="J952">
+        <v>50</v>
+      </c>
+      <c r="K952">
+        <v>1</v>
+      </c>
+      <c r="L952">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="953" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A953" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B953" t="s">
+        <v>2</v>
+      </c>
+      <c r="C953">
+        <v>0</v>
+      </c>
+      <c r="D953">
+        <v>0</v>
+      </c>
+      <c r="E953">
+        <v>6</v>
+      </c>
+      <c r="F953">
+        <v>150</v>
+      </c>
+      <c r="G953">
+        <v>0</v>
+      </c>
+      <c r="H953">
+        <v>0</v>
+      </c>
+      <c r="I953">
+        <v>0</v>
+      </c>
+      <c r="J953">
+        <v>0</v>
+      </c>
+      <c r="K953">
+        <v>1</v>
+      </c>
+      <c r="L953">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="954" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A954" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B954" t="s">
+        <v>3</v>
+      </c>
+      <c r="C954">
+        <v>0</v>
+      </c>
+      <c r="D954">
+        <v>0</v>
+      </c>
+      <c r="E954">
+        <v>25</v>
+      </c>
+      <c r="F954">
+        <v>625</v>
+      </c>
+      <c r="G954">
+        <v>0</v>
+      </c>
+      <c r="H954">
+        <v>0</v>
+      </c>
+      <c r="I954">
+        <v>1</v>
+      </c>
+      <c r="J954">
+        <v>25</v>
+      </c>
+      <c r="K954">
+        <v>2</v>
+      </c>
+      <c r="L954">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="955" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A955" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B955" t="s">
+        <v>2</v>
+      </c>
+      <c r="C955">
+        <v>0</v>
+      </c>
+      <c r="D955">
+        <v>0</v>
+      </c>
+      <c r="E955">
+        <v>5</v>
+      </c>
+      <c r="F955">
+        <v>125</v>
+      </c>
+      <c r="G955">
+        <v>0</v>
+      </c>
+      <c r="H955">
+        <v>0</v>
+      </c>
+      <c r="I955">
+        <v>0</v>
+      </c>
+      <c r="J955">
+        <v>0</v>
+      </c>
+      <c r="K955">
+        <v>1</v>
+      </c>
+      <c r="L955">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="956" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A956" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B956" t="s">
+        <v>3</v>
+      </c>
+      <c r="C956">
+        <v>0</v>
+      </c>
+      <c r="D956">
+        <v>0</v>
+      </c>
+      <c r="E956">
+        <v>26</v>
+      </c>
+      <c r="F956">
+        <v>650</v>
+      </c>
+      <c r="G956">
+        <v>1</v>
+      </c>
+      <c r="H956">
+        <v>15</v>
+      </c>
+      <c r="I956">
+        <v>1</v>
+      </c>
+      <c r="J956">
+        <v>25</v>
+      </c>
+      <c r="K956">
+        <v>2</v>
+      </c>
+      <c r="L956">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="957" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A957" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B957" t="s">
+        <v>2</v>
+      </c>
+      <c r="C957">
+        <v>0</v>
+      </c>
+      <c r="D957">
+        <v>0</v>
+      </c>
+      <c r="E957">
+        <v>7</v>
+      </c>
+      <c r="F957">
+        <v>175</v>
+      </c>
+      <c r="G957">
+        <v>0</v>
+      </c>
+      <c r="H957">
+        <v>0</v>
+      </c>
+      <c r="I957">
+        <v>0</v>
+      </c>
+      <c r="J957">
+        <v>0</v>
+      </c>
+      <c r="K957">
+        <v>0</v>
+      </c>
+      <c r="L957">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="958" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A958" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B958" t="s">
+        <v>3</v>
+      </c>
+      <c r="C958">
+        <v>2</v>
+      </c>
+      <c r="D958">
+        <v>50</v>
+      </c>
+      <c r="E958">
+        <v>23</v>
+      </c>
+      <c r="F958">
+        <v>575</v>
+      </c>
+      <c r="G958">
+        <v>0</v>
+      </c>
+      <c r="H958">
+        <v>0</v>
+      </c>
+      <c r="I958">
+        <v>2</v>
+      </c>
+      <c r="J958">
+        <v>50</v>
+      </c>
+      <c r="K958">
+        <v>3</v>
+      </c>
+      <c r="L958">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="959" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A959" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B959" t="s">
+        <v>2</v>
+      </c>
+      <c r="C959">
+        <v>0</v>
+      </c>
+      <c r="D959">
+        <v>0</v>
+      </c>
+      <c r="E959">
+        <v>6</v>
+      </c>
+      <c r="F959">
+        <v>150</v>
+      </c>
+      <c r="G959">
+        <v>0</v>
+      </c>
+      <c r="H959">
+        <v>0</v>
+      </c>
+      <c r="I959">
+        <v>0</v>
+      </c>
+      <c r="J959">
+        <v>0</v>
+      </c>
+      <c r="K959">
+        <v>1</v>
+      </c>
+      <c r="L959">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="960" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A960" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B960" t="s">
+        <v>3</v>
+      </c>
+      <c r="C960">
+        <v>2</v>
+      </c>
+      <c r="D960">
+        <v>50</v>
+      </c>
+      <c r="E960">
+        <v>19</v>
+      </c>
+      <c r="F960">
+        <v>475</v>
+      </c>
+      <c r="G960">
+        <v>0</v>
+      </c>
+      <c r="H960">
+        <v>0</v>
+      </c>
+      <c r="I960">
+        <v>2</v>
+      </c>
+      <c r="J960">
+        <v>50</v>
+      </c>
+      <c r="K960">
+        <v>2</v>
+      </c>
+      <c r="L960">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="961" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A961" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B961" t="s">
+        <v>2</v>
+      </c>
+      <c r="C961">
+        <v>0</v>
+      </c>
+      <c r="D961">
+        <v>0</v>
+      </c>
+      <c r="E961">
+        <v>7</v>
+      </c>
+      <c r="F961">
+        <v>175</v>
+      </c>
+      <c r="G961">
+        <v>0</v>
+      </c>
+      <c r="H961">
+        <v>0</v>
+      </c>
+      <c r="I961">
+        <v>0</v>
+      </c>
+      <c r="J961">
+        <v>0</v>
+      </c>
+      <c r="K961">
+        <v>0</v>
+      </c>
+      <c r="L961">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="962" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A962" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B962" t="s">
+        <v>3</v>
+      </c>
+      <c r="C962">
+        <v>0</v>
+      </c>
+      <c r="D962">
+        <v>0</v>
+      </c>
+      <c r="E962">
+        <v>18</v>
+      </c>
+      <c r="F962">
+        <v>450</v>
+      </c>
+      <c r="G962">
+        <v>0</v>
+      </c>
+      <c r="H962">
+        <v>0</v>
+      </c>
+      <c r="I962">
+        <v>1</v>
+      </c>
+      <c r="J962">
+        <v>25</v>
+      </c>
+      <c r="K962">
+        <v>2</v>
+      </c>
+      <c r="L962">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="963" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A963" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B963" t="s">
+        <v>2</v>
+      </c>
+      <c r="C963">
+        <v>0</v>
+      </c>
+      <c r="D963">
+        <v>0</v>
+      </c>
+      <c r="E963">
+        <v>5</v>
+      </c>
+      <c r="F963">
+        <v>125</v>
+      </c>
+      <c r="G963">
+        <v>0</v>
+      </c>
+      <c r="H963">
+        <v>0</v>
+      </c>
+      <c r="I963">
+        <v>0</v>
+      </c>
+      <c r="J963">
+        <v>0</v>
+      </c>
+      <c r="K963">
+        <v>0</v>
+      </c>
+      <c r="L963">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="964" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A964" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B964" t="s">
+        <v>3</v>
+      </c>
+      <c r="C964">
+        <v>0</v>
+      </c>
+      <c r="D964">
+        <v>0</v>
+      </c>
+      <c r="E964">
+        <v>18</v>
+      </c>
+      <c r="F964">
+        <v>450</v>
+      </c>
+      <c r="G964">
+        <v>0</v>
+      </c>
+      <c r="H964">
+        <v>0</v>
+      </c>
+      <c r="I964">
+        <v>0</v>
+      </c>
+      <c r="J964">
+        <v>0</v>
+      </c>
+      <c r="K964">
+        <v>0</v>
+      </c>
+      <c r="L964">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="965" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A965" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B965" t="s">
+        <v>2</v>
+      </c>
+      <c r="C965">
+        <v>0</v>
+      </c>
+      <c r="D965">
+        <v>0</v>
+      </c>
+      <c r="E965">
+        <v>7</v>
+      </c>
+      <c r="F965">
+        <v>175</v>
+      </c>
+      <c r="G965">
+        <v>0</v>
+      </c>
+      <c r="H965">
+        <v>0</v>
+      </c>
+      <c r="I965">
+        <v>0</v>
+      </c>
+      <c r="J965">
+        <v>0</v>
+      </c>
+      <c r="K965">
+        <v>1</v>
+      </c>
+      <c r="L965">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="966" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A966" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B966" t="s">
+        <v>3</v>
+      </c>
+      <c r="C966">
+        <v>2</v>
+      </c>
+      <c r="D966">
+        <v>50</v>
+      </c>
+      <c r="E966">
+        <v>19</v>
+      </c>
+      <c r="F966">
+        <v>475</v>
+      </c>
+      <c r="G966">
+        <v>0</v>
+      </c>
+      <c r="H966">
+        <v>0</v>
+      </c>
+      <c r="I966">
+        <v>2</v>
+      </c>
+      <c r="J966">
+        <v>50</v>
+      </c>
+      <c r="K966">
+        <v>4</v>
+      </c>
+      <c r="L966">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="967" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A967" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B967" t="s">
+        <v>2</v>
+      </c>
+      <c r="C967">
+        <v>0</v>
+      </c>
+      <c r="D967">
+        <v>0</v>
+      </c>
+      <c r="E967">
+        <v>6</v>
+      </c>
+      <c r="F967">
+        <v>150</v>
+      </c>
+      <c r="G967">
+        <v>0</v>
+      </c>
+      <c r="H967">
+        <v>0</v>
+      </c>
+      <c r="I967">
+        <v>0</v>
+      </c>
+      <c r="J967">
+        <v>0</v>
+      </c>
+      <c r="K967">
+        <v>1</v>
+      </c>
+      <c r="L967">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="968" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A968" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B968" t="s">
+        <v>3</v>
+      </c>
+      <c r="C968">
+        <v>0</v>
+      </c>
+      <c r="D968">
+        <v>0</v>
+      </c>
+      <c r="E968">
+        <v>21</v>
+      </c>
+      <c r="F968">
+        <v>525</v>
+      </c>
+      <c r="G968">
+        <v>0</v>
+      </c>
+      <c r="H968">
+        <v>0</v>
+      </c>
+      <c r="I968">
+        <v>1</v>
+      </c>
+      <c r="J968">
+        <v>25</v>
+      </c>
+      <c r="K968">
+        <v>1</v>
+      </c>
+      <c r="L968">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="969" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A969" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B969" t="s">
+        <v>2</v>
+      </c>
+      <c r="C969">
+        <v>0</v>
+      </c>
+      <c r="D969">
+        <v>0</v>
+      </c>
+      <c r="E969">
+        <v>8</v>
+      </c>
+      <c r="F969">
+        <v>200</v>
+      </c>
+      <c r="G969">
+        <v>0</v>
+      </c>
+      <c r="H969">
+        <v>0</v>
+      </c>
+      <c r="I969">
+        <v>0</v>
+      </c>
+      <c r="J969">
+        <v>0</v>
+      </c>
+      <c r="K969">
+        <v>0</v>
+      </c>
+      <c r="L969">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="970" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A970" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B970" t="s">
+        <v>3</v>
+      </c>
+      <c r="C970">
+        <v>0</v>
+      </c>
+      <c r="D970">
+        <v>0</v>
+      </c>
+      <c r="E970">
+        <v>18</v>
+      </c>
+      <c r="F970">
+        <v>450</v>
+      </c>
+      <c r="G970">
+        <v>0</v>
+      </c>
+      <c r="H970">
+        <v>0</v>
+      </c>
+      <c r="I970">
+        <v>1</v>
+      </c>
+      <c r="J970">
+        <v>25</v>
+      </c>
+      <c r="K970">
+        <v>2</v>
+      </c>
+      <c r="L970">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="971" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A971" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B971" t="s">
+        <v>2</v>
+      </c>
+      <c r="C971">
+        <v>0</v>
+      </c>
+      <c r="D971">
+        <v>0</v>
+      </c>
+      <c r="E971">
+        <v>8</v>
+      </c>
+      <c r="F971">
+        <v>200</v>
+      </c>
+      <c r="G971">
+        <v>0</v>
+      </c>
+      <c r="H971">
+        <v>0</v>
+      </c>
+      <c r="I971">
+        <v>0</v>
+      </c>
+      <c r="J971">
+        <v>0</v>
+      </c>
+      <c r="K971">
+        <v>1</v>
+      </c>
+      <c r="L971">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="972" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A972" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B972" t="s">
+        <v>3</v>
+      </c>
+      <c r="C972">
+        <v>2</v>
+      </c>
+      <c r="D972">
+        <v>50</v>
+      </c>
+      <c r="E972">
+        <v>18</v>
+      </c>
+      <c r="F972">
+        <v>450</v>
+      </c>
+      <c r="G972">
+        <v>0</v>
+      </c>
+      <c r="H972">
+        <v>0</v>
+      </c>
+      <c r="I972">
+        <v>1</v>
+      </c>
+      <c r="J972">
+        <v>25</v>
+      </c>
+      <c r="K972">
+        <v>2</v>
+      </c>
+      <c r="L972">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="973" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A973" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B973" t="s">
+        <v>2</v>
+      </c>
+      <c r="C973">
+        <v>0</v>
+      </c>
+      <c r="D973">
+        <v>0</v>
+      </c>
+      <c r="E973">
+        <v>6</v>
+      </c>
+      <c r="F973">
+        <v>150</v>
+      </c>
+      <c r="G973">
+        <v>0</v>
+      </c>
+      <c r="H973">
+        <v>0</v>
+      </c>
+      <c r="I973">
+        <v>0</v>
+      </c>
+      <c r="J973">
+        <v>0</v>
+      </c>
+      <c r="K973">
+        <v>0</v>
+      </c>
+      <c r="L973">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="974" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A974" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B974" t="s">
+        <v>3</v>
+      </c>
+      <c r="C974">
+        <v>0</v>
+      </c>
+      <c r="D974">
+        <v>0</v>
+      </c>
+      <c r="E974">
+        <v>18</v>
+      </c>
+      <c r="F974">
+        <v>450</v>
+      </c>
+      <c r="G974">
+        <v>1</v>
+      </c>
+      <c r="H974">
+        <v>15</v>
+      </c>
+      <c r="I974">
+        <v>2</v>
+      </c>
+      <c r="J974">
+        <v>50</v>
+      </c>
+      <c r="K974">
+        <v>2</v>
+      </c>
+      <c r="L974">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="975" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A975" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B975" t="s">
+        <v>2</v>
+      </c>
+      <c r="C975">
+        <v>0</v>
+      </c>
+      <c r="D975">
+        <v>0</v>
+      </c>
+      <c r="E975">
+        <v>5</v>
+      </c>
+      <c r="F975">
+        <v>125</v>
+      </c>
+      <c r="G975">
+        <v>0</v>
+      </c>
+      <c r="H975">
+        <v>0</v>
+      </c>
+      <c r="I975">
+        <v>0</v>
+      </c>
+      <c r="J975">
+        <v>0</v>
+      </c>
+      <c r="K975">
+        <v>1</v>
+      </c>
+      <c r="L975">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="976" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A976" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B976" t="s">
+        <v>3</v>
+      </c>
+      <c r="C976">
+        <v>0</v>
+      </c>
+      <c r="D976">
+        <v>0</v>
+      </c>
+      <c r="E976">
+        <v>18</v>
+      </c>
+      <c r="F976">
+        <v>450</v>
+      </c>
+      <c r="G976">
+        <v>1</v>
+      </c>
+      <c r="H976">
+        <v>15</v>
+      </c>
+      <c r="I976">
+        <v>0</v>
+      </c>
+      <c r="J976">
+        <v>0</v>
+      </c>
+      <c r="K976">
+        <v>1</v>
+      </c>
+      <c r="L976">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="977" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A977" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B977" t="s">
+        <v>2</v>
+      </c>
+      <c r="C977">
+        <v>0</v>
+      </c>
+      <c r="D977">
+        <v>0</v>
+      </c>
+      <c r="E977">
+        <v>8</v>
+      </c>
+      <c r="F977">
+        <v>200</v>
+      </c>
+      <c r="G977">
+        <v>0</v>
+      </c>
+      <c r="H977">
+        <v>0</v>
+      </c>
+      <c r="I977">
+        <v>0</v>
+      </c>
+      <c r="J977">
+        <v>0</v>
+      </c>
+      <c r="K977">
+        <v>1</v>
+      </c>
+      <c r="L977">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="978" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A978" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B978" t="s">
+        <v>3</v>
+      </c>
+      <c r="C978">
+        <v>0</v>
+      </c>
+      <c r="D978">
+        <v>0</v>
+      </c>
+      <c r="E978">
+        <v>18</v>
+      </c>
+      <c r="F978">
+        <v>450</v>
+      </c>
+      <c r="G978">
+        <v>0</v>
+      </c>
+      <c r="H978">
+        <v>0</v>
+      </c>
+      <c r="I978">
+        <v>1</v>
+      </c>
+      <c r="J978">
+        <v>25</v>
+      </c>
+      <c r="K978">
+        <v>3</v>
+      </c>
+      <c r="L978">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="979" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A979" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B979" t="s">
+        <v>2</v>
+      </c>
+      <c r="C979">
+        <v>0</v>
+      </c>
+      <c r="D979">
+        <v>0</v>
+      </c>
+      <c r="E979">
+        <v>5</v>
+      </c>
+      <c r="F979">
+        <v>125</v>
+      </c>
+      <c r="G979">
+        <v>0</v>
+      </c>
+      <c r="H979">
+        <v>0</v>
+      </c>
+      <c r="I979">
+        <v>0</v>
+      </c>
+      <c r="J979">
+        <v>0</v>
+      </c>
+      <c r="K979">
+        <v>1</v>
+      </c>
+      <c r="L979">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="980" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A980" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B980" t="s">
+        <v>3</v>
+      </c>
+      <c r="C980">
+        <v>2</v>
+      </c>
+      <c r="D980">
+        <v>50</v>
+      </c>
+      <c r="E980">
+        <v>19</v>
+      </c>
+      <c r="F980">
+        <v>475</v>
+      </c>
+      <c r="G980">
+        <v>0</v>
+      </c>
+      <c r="H980">
+        <v>0</v>
+      </c>
+      <c r="I980">
+        <v>0</v>
+      </c>
+      <c r="J980">
+        <v>0</v>
+      </c>
+      <c r="K980">
+        <v>2</v>
+      </c>
+      <c r="L980">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="981" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A981" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B981" t="s">
+        <v>2</v>
+      </c>
+      <c r="C981">
+        <v>0</v>
+      </c>
+      <c r="D981">
+        <v>0</v>
+      </c>
+      <c r="E981">
+        <v>7</v>
+      </c>
+      <c r="F981">
+        <v>175</v>
+      </c>
+      <c r="G981">
+        <v>0</v>
+      </c>
+      <c r="H981">
+        <v>0</v>
+      </c>
+      <c r="I981">
+        <v>0</v>
+      </c>
+      <c r="J981">
+        <v>0</v>
+      </c>
+      <c r="K981">
+        <v>0</v>
+      </c>
+      <c r="L981">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="982" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A982" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B982" t="s">
+        <v>3</v>
+      </c>
+      <c r="C982">
+        <v>1</v>
+      </c>
+      <c r="D982">
+        <v>25</v>
+      </c>
+      <c r="E982">
+        <v>21</v>
+      </c>
+      <c r="F982">
+        <v>525</v>
+      </c>
+      <c r="G982">
+        <v>0</v>
+      </c>
+      <c r="H982">
+        <v>0</v>
+      </c>
+      <c r="I982">
+        <v>3</v>
+      </c>
+      <c r="J982">
+        <v>75</v>
+      </c>
+      <c r="K982">
+        <v>3</v>
+      </c>
+      <c r="L982">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="983" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A983" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B983" t="s">
+        <v>2</v>
+      </c>
+      <c r="C983">
+        <v>0</v>
+      </c>
+      <c r="D983">
+        <v>0</v>
+      </c>
+      <c r="E983">
+        <v>5</v>
+      </c>
+      <c r="F983">
+        <v>125</v>
+      </c>
+      <c r="G983">
+        <v>0</v>
+      </c>
+      <c r="H983">
+        <v>0</v>
+      </c>
+      <c r="I983">
+        <v>0</v>
+      </c>
+      <c r="J983">
+        <v>0</v>
+      </c>
+      <c r="K983">
+        <v>0</v>
+      </c>
+      <c r="L983">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A984" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B984" t="s">
+        <v>3</v>
+      </c>
+      <c r="C984">
+        <v>0</v>
+      </c>
+      <c r="D984">
+        <v>0</v>
+      </c>
+      <c r="E984">
+        <v>16</v>
+      </c>
+      <c r="F984">
+        <v>400</v>
+      </c>
+      <c r="G984">
+        <v>0</v>
+      </c>
+      <c r="H984">
+        <v>0</v>
+      </c>
+      <c r="I984">
+        <v>1</v>
+      </c>
+      <c r="J984">
+        <v>25</v>
+      </c>
+      <c r="K984">
+        <v>2</v>
+      </c>
+      <c r="L984">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="985" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A985" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B985" t="s">
+        <v>2</v>
+      </c>
+      <c r="C985">
+        <v>0</v>
+      </c>
+      <c r="D985">
+        <v>0</v>
+      </c>
+      <c r="E985">
+        <v>7</v>
+      </c>
+      <c r="F985">
+        <v>175</v>
+      </c>
+      <c r="G985">
+        <v>0</v>
+      </c>
+      <c r="H985">
+        <v>0</v>
+      </c>
+      <c r="I985">
+        <v>0</v>
+      </c>
+      <c r="J985">
+        <v>0</v>
+      </c>
+      <c r="K985">
+        <v>1</v>
+      </c>
+      <c r="L985">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="986" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A986" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B986" t="s">
+        <v>3</v>
+      </c>
+      <c r="C986">
+        <v>0</v>
+      </c>
+      <c r="D986">
+        <v>0</v>
+      </c>
+      <c r="E986">
+        <v>18</v>
+      </c>
+      <c r="F986">
+        <v>450</v>
+      </c>
+      <c r="G986">
+        <v>0</v>
+      </c>
+      <c r="H986">
+        <v>0</v>
+      </c>
+      <c r="I986">
+        <v>1</v>
+      </c>
+      <c r="J986">
+        <v>25</v>
+      </c>
+      <c r="K986">
+        <v>2</v>
+      </c>
+      <c r="L986">
         <v>50</v>
       </c>
     </row>
